--- a/tests/fixtures/hucre-report.xlsx
+++ b/tests/fixtures/hucre-report.xlsx
@@ -62,7 +62,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor/>
+        <fgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
